--- a/Assets/ExcelData/MonsterTable.xlsx
+++ b/Assets/ExcelData/MonsterTable.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D2CA1C-B125-4F63-BAF5-E3E6195FA262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2542995-32C6-4898-ADD5-8105A90C42D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
     <sheet name="MonsterLevelByStat" sheetId="2" r:id="rId2"/>
+    <sheet name="MapMonsterConfig" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>monsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,10 +108,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Multiplier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Dungeon_Droid_Helmet_AR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,6 +117,90 @@
   </si>
   <si>
     <t>Dungeon_Droid_Helmet_Tank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHPRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefenseRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증가율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 증가율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 증가율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Field</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalMonsterLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EliteMonsterLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보토스 뒷골목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreditReward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreditRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크레딧 증가율</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,10 +244,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,21 +532,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="2" width="54.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="11.625" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="2" max="2" width="46.375" customWidth="1"/>
+    <col min="3" max="5" width="20.125" customWidth="1"/>
+    <col min="6" max="6" width="12.25" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -473,25 +558,34 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -501,24 +595,35 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1">
         <v>2000</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="1">
+      <c r="I2" s="1">
         <v>5</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
+        <v>101</v>
+      </c>
+      <c r="K2" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="L2" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -528,24 +633,35 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1">
         <v>2500</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>250</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="1">
+      <c r="I3" s="1">
         <v>5</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
+        <v>101</v>
+      </c>
+      <c r="K3" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="L3" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -555,105 +671,149 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1">
         <v>10000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>500</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="G4" s="1">
+      <c r="I4" s="1">
         <v>5</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
+        <v>102</v>
+      </c>
+      <c r="K4" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="L4" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1">
         <v>2000</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>15</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>5</v>
       </c>
-      <c r="G5" s="1">
+      <c r="I5" s="1">
         <v>5</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
         <v>2500</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>250</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>5</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1">
         <v>10000</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>500</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>20</v>
+      </c>
+      <c r="L7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3000</v>
       </c>
@@ -663,24 +823,35 @@
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1">
         <v>40000</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>500</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -690,8 +861,10 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -701,8 +874,10 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -712,8 +887,10 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -723,8 +900,10 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -734,8 +913,10 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -745,8 +926,10 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -756,8 +939,10 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -767,8 +952,10 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -778,6 +965,8 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -787,289 +976,805 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77FCFDF-1279-4DFD-A519-64CEEBE26844}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="23.75" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f>ROUND(B2*1.05, 2)</f>
+        <f>ROUND(B2 * $G$2,2)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C3" s="1">
+        <f>ROUND(C2 * $G$4,2)</f>
         <v>1.05</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" s="1">
+        <f>ROUND(D2 * $G$6,2)</f>
+        <v>1.02</v>
+      </c>
+      <c r="E3" s="1">
+        <f>ROUND(E2 * $G$8,2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" ref="B4:B31" si="0">ROUND(B3*1.05, 2)</f>
+        <f t="shared" ref="B4:B31" si="0">ROUND(B3 * $G$2,2)</f>
+        <v>1.21</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:C30" si="1">ROUND(C3 * $G$4,2)</f>
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D31" si="2">ROUND(D3 * $G$6,2)</f>
+        <v>1.04</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E30" si="3">ROUND(E3 * $G$8,2)</f>
+        <v>1.44</v>
+      </c>
+      <c r="G4">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
+        <v>1.33</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.06</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="3"/>
+        <v>1.73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
+        <v>1.46</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
         <v>1.22</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D6" s="1">
+        <f t="shared" si="2"/>
+        <v>1.08</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="3"/>
+        <v>2.08</v>
+      </c>
+      <c r="G6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
+        <v>1.61</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
         <v>1.28</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
+        <v>1.77</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
         <v>1.34</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D8" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
+        <v>1.95</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
         <v>1.41</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="3"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
+        <v>2.15</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
         <v>1.48</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D10" s="1">
+        <f t="shared" si="2"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="3"/>
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
+        <v>2.37</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
         <v>1.55</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D11" s="1">
+        <f t="shared" si="2"/>
+        <v>1.18</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="3"/>
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
+        <v>2.61</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
         <v>1.63</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D12" s="1">
+        <f t="shared" si="2"/>
+        <v>1.2</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="3"/>
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
+        <v>2.87</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D13" s="1">
+        <f t="shared" si="2"/>
+        <v>1.22</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="3"/>
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
+        <v>3.16</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D14" s="1">
+        <f t="shared" si="2"/>
+        <v>1.24</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="3"/>
+        <v>8.9499999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
+        <v>3.48</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
         <v>1.89</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D15" s="1">
+        <f t="shared" si="2"/>
+        <v>1.26</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="3"/>
+        <v>10.74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
+        <v>3.83</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D16" s="1">
+        <f t="shared" si="2"/>
+        <v>1.29</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="3"/>
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
+        <v>4.21</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
         <v>2.08</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D17" s="1">
+        <f t="shared" si="2"/>
+        <v>1.32</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="3"/>
+        <v>15.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
+        <v>4.63</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
         <v>2.1800000000000002</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D18" s="1">
+        <f t="shared" si="2"/>
+        <v>1.35</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="3"/>
+        <v>18.559999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
+        <v>5.09</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
         <v>2.29</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D19" s="1">
+        <f t="shared" si="2"/>
+        <v>1.38</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="3"/>
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
+        <v>5.6</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D20" s="1">
+        <f t="shared" si="2"/>
+        <v>1.41</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="3"/>
+        <v>26.72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
+        <v>6.16</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
         <v>2.52</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D21" s="1">
+        <f t="shared" si="2"/>
+        <v>1.44</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="3"/>
+        <v>32.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
+        <v>6.78</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
         <v>2.65</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D22" s="1">
+        <f t="shared" si="2"/>
+        <v>1.47</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="3"/>
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
+        <v>7.46</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
         <v>2.78</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D23" s="1">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="3"/>
+        <v>46.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
         <v>2.92</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D24" s="1">
+        <f t="shared" si="2"/>
+        <v>1.53</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="3"/>
+        <v>55.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
         <v>3.07</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D25" s="1">
+        <f t="shared" si="2"/>
+        <v>1.56</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="3"/>
+        <v>66.47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
+        <v>9.93</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
         <v>3.22</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D26" s="1">
+        <f t="shared" si="2"/>
+        <v>1.59</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="3"/>
+        <v>79.760000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
+        <v>10.92</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
         <v>3.38</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D27" s="1">
+        <f t="shared" si="2"/>
+        <v>1.62</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="3"/>
+        <v>95.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
+        <v>12.01</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
         <v>3.55</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D28" s="1">
+        <f t="shared" si="2"/>
+        <v>1.65</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="3"/>
+        <v>114.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
+        <v>13.21</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
         <v>3.73</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D29" s="1">
+        <f t="shared" si="2"/>
+        <v>1.68</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="3"/>
+        <v>137.82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
+        <v>14.53</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
         <v>3.92</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D30" s="1">
+        <f t="shared" si="2"/>
+        <v>1.71</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="3"/>
+        <v>165.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
+        <v>15.98</v>
+      </c>
+      <c r="C31" s="1">
+        <f>ROUND(C30 * $G$4,2)</f>
         <v>4.12</v>
       </c>
+      <c r="D31" s="1">
+        <f t="shared" si="2"/>
+        <v>1.74</v>
+      </c>
+      <c r="E31" s="1">
+        <f>ROUND(E30 * $G$8,2)</f>
+        <v>198.46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2644EC05-92F5-47AD-834C-2BAE3E05A5BF}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="19.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/ExcelData/MonsterTable.xlsx
+++ b/Assets/ExcelData/MonsterTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2542995-32C6-4898-ADD5-8105A90C42D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAA5038-3902-4337-957D-C5F40A01CE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>monsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -201,6 +201,14 @@
   </si>
   <si>
     <t>크레딧 증가율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보토스 뒷골목 깊은 곳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예로니무스 토벌전</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1689,7 +1697,7 @@
         <v>1000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
         <v>5</v>
@@ -1699,40 +1707,88 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="A3" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="1">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="A4" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="A6" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="A7" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="A8" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>

--- a/Assets/ExcelData/MonsterTable.xlsx
+++ b/Assets/ExcelData/MonsterTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAA5038-3902-4337-957D-C5F40A01CE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2562BBE0-B2A2-4142-9BF2-6DED77BEB972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>

--- a/Assets/ExcelData/MonsterTable.xlsx
+++ b/Assets/ExcelData/MonsterTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2562BBE0-B2A2-4142-9BF2-6DED77BEB972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280D3D14-0A97-4916-9F2E-5F16DFFC471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,7 +613,7 @@
         <v>2000</v>
       </c>
       <c r="G2" s="1">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -727,7 +727,7 @@
         <v>2000</v>
       </c>
       <c r="G5" s="1">
-        <v>15</v>
+        <v>550</v>
       </c>
       <c r="H5" s="1">
         <v>5</v>

--- a/Assets/ExcelData/MonsterTable.xlsx
+++ b/Assets/ExcelData/MonsterTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280D3D14-0A97-4916-9F2E-5F16DFFC471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F32CA36-4609-4CE7-8986-5A1419EED150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28380" yWindow="4095" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
@@ -613,7 +613,7 @@
         <v>2000</v>
       </c>
       <c r="G2" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -651,7 +651,7 @@
         <v>2500</v>
       </c>
       <c r="G3" s="1">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -689,7 +689,7 @@
         <v>10000</v>
       </c>
       <c r="G4" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H4" s="1">
         <v>5</v>
@@ -727,7 +727,7 @@
         <v>2000</v>
       </c>
       <c r="G5" s="1">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1">
         <v>5</v>
